--- a/xlsx/換色紀錄表(9_1).xlsx
+++ b/xlsx/換色紀錄表(9_1).xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="214" documentId="11_4FBE7C339D0C5806B5E87E471C75590E52E680CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AD07802-BFD7-734C-9742-676C387E1497}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{A066A97B-C0F9-7645-9D9D-7DFA57881DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="29699" windowHeight="12050" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="E2" s="30">
         <f ca="1">TODAY()</f>
-        <v>45201</v>
+        <v>46300</v>
       </c>
       <c r="F2" s="149" t="str">
         <f ca="1">TEXT(WEEKDAY(E2,1),"aaaa")</f>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G2" s="30">
         <f ca="1">TODAY()</f>
-        <v>45201</v>
+        <v>46300</v>
       </c>
       <c r="H2" s="83" t="str">
         <f ca="1">TEXT(WEEKDAY(每日用粉紀錄表!E2,1),"aaaa")</f>
